--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>P. ISERN MAZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>40.245</v>
+        <v>34.63339999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>32.7474</v>
+        <v>31.1727</v>
       </c>
       <c r="F2" t="n">
-        <v>7.497999999999999</v>
+        <v>3.4611</v>
       </c>
       <c r="G2" t="n">
-        <v>7.849600000000001</v>
+        <v>24.8758</v>
       </c>
       <c r="H2" t="n">
-        <v>19.3097</v>
+        <v>19.8</v>
       </c>
       <c r="I2" t="n">
-        <v>-11.4602</v>
+        <v>5.075699999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>33.4846</v>
+        <v>46.2383</v>
       </c>
       <c r="K2" t="n">
-        <v>33.1231</v>
+        <v>32.1252</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3612999999999999</v>
+        <v>14.1134</v>
       </c>
       <c r="M2" t="n">
-        <v>-25.6348</v>
+        <v>-21.3623</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.8134</v>
+        <v>-12.3248</v>
       </c>
       <c r="O2" t="n">
-        <v>-11.8213</v>
+        <v>-9.037699999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.248800000000001</v>
+        <v>-12.487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-44.7456</v>
+        <v>-48.6998</v>
       </c>
       <c r="R2" t="n">
-        <v>45.9941</v>
+        <v>36.2126</v>
       </c>
       <c r="S2" t="n">
-        <v>12.3071</v>
+        <v>-4.7674</v>
       </c>
       <c r="T2" t="n">
-        <v>8.487300000000001</v>
+        <v>-4.9298</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8198</v>
+        <v>0.1622000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>18.8394</v>
+        <v>27.0124</v>
       </c>
       <c r="W2" t="n">
-        <v>35.521</v>
+        <v>38.5636</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.6814</v>
+        <v>-11.5516</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ISERN MAZA</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7321</v>
+        <v>32.7083</v>
       </c>
       <c r="E3" t="n">
-        <v>24.8412</v>
+        <v>26.6119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8908999999999994</v>
+        <v>6.0961</v>
       </c>
       <c r="G3" t="n">
-        <v>24.8758</v>
+        <v>7.849600000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>19.8</v>
+        <v>19.3097</v>
       </c>
       <c r="I3" t="n">
-        <v>5.075699999999999</v>
+        <v>-11.4602</v>
       </c>
       <c r="J3" t="n">
-        <v>46.2383</v>
+        <v>33.4846</v>
       </c>
       <c r="K3" t="n">
-        <v>32.1252</v>
+        <v>33.1231</v>
       </c>
       <c r="L3" t="n">
-        <v>14.1134</v>
+        <v>0.3612999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-21.3623</v>
+        <v>-25.6348</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.3248</v>
+        <v>-13.8134</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.037699999999999</v>
+        <v>-11.8213</v>
       </c>
       <c r="P3" t="n">
-        <v>-12.487</v>
+        <v>1.248800000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48.6998</v>
+        <v>-44.7456</v>
       </c>
       <c r="R3" t="n">
-        <v>36.2126</v>
+        <v>45.9941</v>
       </c>
       <c r="S3" t="n">
-        <v>-13.6692</v>
+        <v>4.7701</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.2615</v>
+        <v>2.352</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.4076</v>
+        <v>2.4183</v>
       </c>
       <c r="V3" t="n">
-        <v>27.0124</v>
+        <v>18.8394</v>
       </c>
       <c r="W3" t="n">
-        <v>38.5636</v>
+        <v>35.521</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.5516</v>
+        <v>-16.6814</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>22.5366</v>
+        <v>30.304</v>
       </c>
       <c r="E4" t="n">
-        <v>15.1263</v>
+        <v>41.0626</v>
       </c>
       <c r="F4" t="n">
-        <v>7.410399999999999</v>
+        <v>-10.7586</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5798</v>
+        <v>12.8527</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.901</v>
+        <v>5.7549</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4809</v>
+        <v>7.098400000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>18.9948</v>
+        <v>42.6259</v>
       </c>
       <c r="K4" t="n">
-        <v>7.423900000000001</v>
+        <v>20.9958</v>
       </c>
       <c r="L4" t="n">
-        <v>11.571</v>
+        <v>21.6299</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.4151</v>
+        <v>-29.7732</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.3249</v>
+        <v>-15.2411</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.09</v>
+        <v>-14.532</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.6141</v>
+        <v>10.406</v>
       </c>
       <c r="Q4" t="n">
-        <v>-41.6237</v>
+        <v>-36.4209</v>
       </c>
       <c r="R4" t="n">
-        <v>31.0094</v>
+        <v>46.8268</v>
       </c>
       <c r="S4" t="n">
-        <v>27.7873</v>
+        <v>-4.134600000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>20.4014</v>
+        <v>-2.3266</v>
       </c>
       <c r="U4" t="n">
-        <v>7.3858</v>
+        <v>-1.8081</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7831</v>
+        <v>11.1801</v>
       </c>
       <c r="W4" t="n">
-        <v>17.3539</v>
+        <v>37.184</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.5706</v>
+        <v>-26.0042</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>20.8263</v>
+        <v>26.4546</v>
       </c>
       <c r="E5" t="n">
-        <v>35.3504</v>
+        <v>13.4498</v>
       </c>
       <c r="F5" t="n">
-        <v>-14.5241</v>
+        <v>13.0044</v>
       </c>
       <c r="G5" t="n">
-        <v>12.8527</v>
+        <v>9.982900000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7549</v>
+        <v>-0.9463999999999992</v>
       </c>
       <c r="I5" t="n">
-        <v>7.098400000000001</v>
+        <v>10.9293</v>
       </c>
       <c r="J5" t="n">
-        <v>42.6259</v>
+        <v>36.2628</v>
       </c>
       <c r="K5" t="n">
-        <v>20.9958</v>
+        <v>16.2919</v>
       </c>
       <c r="L5" t="n">
-        <v>21.6299</v>
+        <v>19.9709</v>
       </c>
       <c r="M5" t="n">
-        <v>-29.7732</v>
+        <v>-26.2798</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.2411</v>
+        <v>-17.238</v>
       </c>
       <c r="O5" t="n">
-        <v>-14.532</v>
+        <v>-9.041499999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>10.406</v>
+        <v>-3.329800000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.4209</v>
+        <v>-54.3189</v>
       </c>
       <c r="R5" t="n">
-        <v>46.8268</v>
+        <v>50.9891</v>
       </c>
       <c r="S5" t="n">
-        <v>-13.6126</v>
+        <v>-4.0057</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.0388</v>
+        <v>-4.0325</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.5735</v>
+        <v>0.02719999999999996</v>
       </c>
       <c r="V5" t="n">
-        <v>11.1801</v>
+        <v>23.8071</v>
       </c>
       <c r="W5" t="n">
-        <v>37.184</v>
+        <v>35.539</v>
       </c>
       <c r="X5" t="n">
-        <v>-26.0042</v>
+        <v>-11.732</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>17.9591</v>
+        <v>16.3434</v>
       </c>
       <c r="E6" t="n">
-        <v>22.0723</v>
+        <v>19.1883</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.1129</v>
+        <v>-2.8448</v>
       </c>
       <c r="G6" t="n">
         <v>8.280200000000001</v>
@@ -922,13 +922,13 @@
         <v>27.4717</v>
       </c>
       <c r="S6" t="n">
-        <v>4.306</v>
+        <v>2.6907</v>
       </c>
       <c r="T6" t="n">
-        <v>5.9091</v>
+        <v>3.0256</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.603</v>
+        <v>-0.3351000000000002</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0792</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>12.1381</v>
+        <v>12.6609</v>
       </c>
       <c r="E7" t="n">
-        <v>4.392600000000001</v>
+        <v>8.473599999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>7.745200000000001</v>
+        <v>4.1875</v>
       </c>
       <c r="G7" t="n">
-        <v>9.982900000000001</v>
+        <v>-3.531999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9463999999999992</v>
+        <v>8.167300000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>10.9293</v>
+        <v>-11.6994</v>
       </c>
       <c r="J7" t="n">
-        <v>36.2628</v>
+        <v>17.5975</v>
       </c>
       <c r="K7" t="n">
-        <v>16.2919</v>
+        <v>19.9979</v>
       </c>
       <c r="L7" t="n">
-        <v>19.9709</v>
+        <v>-2.4006</v>
       </c>
       <c r="M7" t="n">
-        <v>-26.2798</v>
+        <v>-21.1295</v>
       </c>
       <c r="N7" t="n">
-        <v>-17.238</v>
+        <v>-11.8309</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.041499999999999</v>
+        <v>-9.2988</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.329800000000001</v>
+        <v>16.2331</v>
       </c>
       <c r="Q7" t="n">
-        <v>-54.3189</v>
+        <v>-16.6495</v>
       </c>
       <c r="R7" t="n">
-        <v>50.9891</v>
+        <v>32.8827</v>
       </c>
       <c r="S7" t="n">
-        <v>-18.3219</v>
+        <v>-3.5072</v>
       </c>
       <c r="T7" t="n">
-        <v>-13.0902</v>
+        <v>-2.4338</v>
       </c>
       <c r="U7" t="n">
-        <v>-5.2323</v>
+        <v>-1.0734</v>
       </c>
       <c r="V7" t="n">
-        <v>23.8071</v>
+        <v>3.4671</v>
       </c>
       <c r="W7" t="n">
-        <v>35.539</v>
+        <v>9.9595</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.732</v>
+        <v>-6.4921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>11.7873</v>
+        <v>6.666200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5755</v>
+        <v>15.6084</v>
       </c>
       <c r="F8" t="n">
-        <v>6.2116</v>
+        <v>-8.9421</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.531999999999999</v>
+        <v>16.967</v>
       </c>
       <c r="H8" t="n">
-        <v>8.167300000000001</v>
+        <v>1.931</v>
       </c>
       <c r="I8" t="n">
-        <v>-11.6994</v>
+        <v>15.036</v>
       </c>
       <c r="J8" t="n">
-        <v>17.5975</v>
+        <v>40.6088</v>
       </c>
       <c r="K8" t="n">
-        <v>19.9979</v>
+        <v>13.7351</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.4006</v>
+        <v>26.874</v>
       </c>
       <c r="M8" t="n">
-        <v>-21.1295</v>
+        <v>-23.6418</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.8309</v>
+        <v>-11.8041</v>
       </c>
       <c r="O8" t="n">
-        <v>-9.2988</v>
+        <v>-11.8378</v>
       </c>
       <c r="P8" t="n">
-        <v>16.2331</v>
+        <v>-5.6193</v>
       </c>
       <c r="Q8" t="n">
-        <v>-16.6495</v>
+        <v>-48.908</v>
       </c>
       <c r="R8" t="n">
-        <v>32.8827</v>
+        <v>43.2885</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.3814</v>
+        <v>-9.638400000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.3318</v>
+        <v>-3.6001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9502999999999997</v>
+        <v>-6.038</v>
       </c>
       <c r="V8" t="n">
-        <v>3.4671</v>
+        <v>4.9566</v>
       </c>
       <c r="W8" t="n">
-        <v>9.9595</v>
+        <v>27.5077</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.4921</v>
+        <v>-22.5512</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CARREÑO VIDAL</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>3.3125</v>
+        <v>6.3966</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9603</v>
+        <v>2.188599999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3521</v>
+        <v>4.2081</v>
       </c>
       <c r="G9" t="n">
-        <v>4.0024</v>
+        <v>3.5798</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-3.901</v>
       </c>
       <c r="I9" t="n">
-        <v>4.096</v>
+        <v>7.4809</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9985</v>
+        <v>18.9948</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.273</v>
+        <v>7.423900000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>4.2715</v>
+        <v>11.571</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003899999999999994</v>
+        <v>-15.4151</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1795</v>
+        <v>-11.3249</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1755</v>
+        <v>-4.09</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6649</v>
+        <v>-10.6141</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-41.6237</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4569</v>
+        <v>31.0094</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1924</v>
+        <v>11.6473</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3138</v>
+        <v>7.4636</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1214</v>
+        <v>4.184</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1675</v>
+        <v>1.7831</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3975</v>
+        <v>17.3539</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>-15.5706</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>P. CARREÑO VIDAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.683999999999999</v>
+        <v>3.634</v>
       </c>
       <c r="E10" t="n">
-        <v>6.522500000000001</v>
+        <v>2.2818</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.8385</v>
+        <v>1.3522</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.720599999999999</v>
+        <v>4.0024</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6203</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.3409</v>
+        <v>4.096</v>
       </c>
       <c r="J10" t="n">
-        <v>12.0636</v>
+        <v>3.9985</v>
       </c>
       <c r="K10" t="n">
-        <v>9.016</v>
+        <v>-0.273</v>
       </c>
       <c r="L10" t="n">
-        <v>3.048</v>
+        <v>4.2715</v>
       </c>
       <c r="M10" t="n">
-        <v>-14.7843</v>
+        <v>0.003899999999999994</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.395799999999999</v>
+        <v>0.1795</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.388299999999999</v>
+        <v>-0.1755</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.6649</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.4569</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-22.0607</v>
-      </c>
-      <c r="R10" t="n">
-        <v>23.5174</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.9974</v>
+        <v>0.129</v>
       </c>
       <c r="T10" t="n">
-        <v>6.7366</v>
+        <v>0.007599999999999996</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.7393</v>
+        <v>0.1214</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.04949999999999988</v>
+        <v>1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>9.782500000000001</v>
+        <v>1.3975</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.832100000000001</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7712</v>
+        <v>1.992</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3578</v>
+        <v>2.6374</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5866</v>
+        <v>-0.6454</v>
       </c>
       <c r="G11" t="n">
         <v>3.2223</v>
@@ -1312,13 +1312,13 @@
         <v>2.7056</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2192000000000001</v>
+        <v>0.001700000000000035</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3047</v>
+        <v>-0.0252</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08559999999999998</v>
+        <v>0.02690000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6888</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1096</v>
+        <v>-0.2601</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8794000000000001</v>
+        <v>-0.7070000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7698</v>
+        <v>0.4468</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6554</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3595</v>
+        <v>0.209</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2609</v>
+        <v>-0.0885</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.2975</v>
       </c>
       <c r="V12" t="n">
         <v>0.3538</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7302</v>
+        <v>-0.5914</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0979</v>
+        <v>-0.4238999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8281</v>
+        <v>-0.1675</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2518</v>
+        <v>-0.3771</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1923</v>
+        <v>0.3005</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05959999999999996</v>
+        <v>-0.6776</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4521</v>
+        <v>-0.5077</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.2067</v>
       </c>
       <c r="L13" t="n">
-        <v>0.627</v>
+        <v>-0.7144</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2002</v>
+        <v>0.1306</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3672</v>
+        <v>0.0939</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5674000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6243000000000001</v>
+        <v>0.4162</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6243000000000001</v>
+        <v>0.4162</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6251</v>
+        <v>-0.6305000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6458</v>
+        <v>0.08390000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2709</v>
+        <v>-0.7144</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8057000000000001</v>
+        <v>-1.304</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6382</v>
+        <v>1.3479</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1675</v>
+        <v>-2.6519</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3771</v>
+        <v>1.2518</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3005</v>
+        <v>1.1923</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6776</v>
+        <v>0.05959999999999996</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5077</v>
+        <v>1.4521</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2067</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7144</v>
+        <v>0.627</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1306</v>
+        <v>-0.2002</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0939</v>
+        <v>0.3672</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0368</v>
+        <v>-0.5674000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4162</v>
+        <v>0.6243000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4162</v>
+        <v>0.6243000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8448</v>
+        <v>-1.199</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1304</v>
+        <v>-0.1043</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7144</v>
+        <v>-1.0947</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.934</v>
+        <v>-1.4633</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3284</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6056</v>
+        <v>-0.8862000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1168</v>
+        <v>-1.6093</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1322</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.249</v>
+        <v>-0.8205</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0384</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0384</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L15" t="n">
+        <v>-0.7144</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.9717</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.8656</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.1061</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>-0.1551</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.0939</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.249</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-1.8731</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R15" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2857</v>
+        <v>-0.2702</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7144</v>
+        <v>0.06050000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4286</v>
+        <v>-0.3307</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.974</v>
+        <v>-2.0205</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0291</v>
+        <v>1.1738</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9449000000000001</v>
+        <v>-3.194400000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6093</v>
+        <v>-2.720599999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7887999999999999</v>
+        <v>2.6203</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8205</v>
+        <v>-5.3409</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6375999999999999</v>
+        <v>12.0636</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07679999999999999</v>
+        <v>9.016</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7144</v>
+        <v>3.048</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9717</v>
+        <v>-14.7843</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8656</v>
+        <v>-6.395799999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1061</v>
+        <v>-8.388299999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>1.4569</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-22.0607</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4162</v>
+        <v>23.5174</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7809999999999999</v>
+        <v>-0.7071999999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3914</v>
+        <v>1.3882</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3894</v>
+        <v>-2.0956</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.04949999999999988</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>9.782500000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-9.832100000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.900800000000001</v>
+        <v>-2.2555</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3034</v>
+        <v>-1.6499</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.2043</v>
+        <v>-0.6056</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.7025</v>
+        <v>-0.1168</v>
       </c>
       <c r="H17" t="n">
-        <v>-9.864599999999999</v>
+        <v>0.1322</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.837899999999999</v>
+        <v>-0.249</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4132999999999998</v>
+        <v>0.0384</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5002</v>
+        <v>0.0384</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0868</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-13.1157</v>
+        <v>-0.1551</v>
       </c>
       <c r="N17" t="n">
-        <v>-11.3649</v>
+        <v>0.0939</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7512</v>
+        <v>-0.249</v>
       </c>
       <c r="P17" t="n">
-        <v>7.2841</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q17" t="n">
-        <v>-23.3094</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>30.5933</v>
+        <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>7.143199999999999</v>
+        <v>-0.0357</v>
       </c>
       <c r="T17" t="n">
-        <v>7.3413</v>
+        <v>0.3929</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1981000000000002</v>
+        <v>-0.4286</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.625500000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>16.8583</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-22.4839</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0654</v>
+        <v>-3.8702</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4501</v>
+        <v>-2.343</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6152</v>
+        <v>-1.5272</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4751</v>
@@ -1858,13 +1858,13 @@
         <v>0.4162</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.839</v>
+        <v>-0.6438</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3262</v>
+        <v>-0.219</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5127</v>
+        <v>-0.4247</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.2535</v>
+        <v>-5.7963</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.2711</v>
+        <v>-4.3129</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9825</v>
+        <v>-1.4833</v>
       </c>
       <c r="G19" t="n">
         <v>-4.542400000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0.8324</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9193</v>
+        <v>-0.462</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1744</v>
+        <v>-0.2162</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.745</v>
+        <v>-0.2459</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5838</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.6345</v>
+        <v>-6.5105</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5198</v>
+        <v>-3.061999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.1546</v>
+        <v>-3.4486</v>
       </c>
       <c r="G20" t="n">
-        <v>16.967</v>
+        <v>-12.7025</v>
       </c>
       <c r="H20" t="n">
-        <v>1.931</v>
+        <v>-9.864599999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>15.036</v>
+        <v>-2.837899999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>40.6088</v>
+        <v>0.4132999999999998</v>
       </c>
       <c r="K20" t="n">
-        <v>13.7351</v>
+        <v>1.5002</v>
       </c>
       <c r="L20" t="n">
-        <v>26.874</v>
+        <v>-1.0868</v>
       </c>
       <c r="M20" t="n">
-        <v>-23.6418</v>
+        <v>-13.1157</v>
       </c>
       <c r="N20" t="n">
-        <v>-11.8041</v>
+        <v>-11.3649</v>
       </c>
       <c r="O20" t="n">
-        <v>-11.8378</v>
+        <v>-1.7512</v>
       </c>
       <c r="P20" t="n">
-        <v>-5.6193</v>
+        <v>7.2841</v>
       </c>
       <c r="Q20" t="n">
-        <v>-48.908</v>
+        <v>-23.3094</v>
       </c>
       <c r="R20" t="n">
-        <v>43.2885</v>
+        <v>30.5933</v>
       </c>
       <c r="S20" t="n">
-        <v>-28.9396</v>
+        <v>4.5335</v>
       </c>
       <c r="T20" t="n">
-        <v>-17.6895</v>
+        <v>2.9759</v>
       </c>
       <c r="U20" t="n">
-        <v>-11.25</v>
+        <v>1.5575</v>
       </c>
       <c r="V20" t="n">
-        <v>4.9566</v>
+        <v>-5.625500000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>27.5077</v>
+        <v>16.8583</v>
       </c>
       <c r="X20" t="n">
-        <v>-22.5512</v>
+        <v>-22.4839</v>
       </c>
     </row>
     <row r="21">
@@ -2047,22 +2047,22 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>126.5845</v>
+        <v>147.7216</v>
       </c>
       <c r="E21" t="n">
-        <v>145.2711</v>
+        <v>152.121</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.68680000000001</v>
+        <v>-4.399400000000004</v>
       </c>
       <c r="G21" t="n">
-        <v>63.13330000000001</v>
+        <v>63.13329999999999</v>
       </c>
       <c r="H21" t="n">
         <v>66.1953</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.061099999999996</v>
+        <v>-3.061099999999999</v>
       </c>
       <c r="J21" t="n">
         <v>274.7855</v>
@@ -2071,7 +2071,7 @@
         <v>188.4106</v>
       </c>
       <c r="L21" t="n">
-        <v>86.3753</v>
+        <v>86.37529999999998</v>
       </c>
       <c r="M21" t="n">
         <v>-211.6512</v>
@@ -2080,7 +2080,7 @@
         <v>-122.2148</v>
       </c>
       <c r="O21" t="n">
-        <v>-89.43599999999999</v>
+        <v>-89.43599999999998</v>
       </c>
       <c r="P21" t="n">
         <v>11.4465</v>
@@ -2092,13 +2092,13 @@
         <v>376.694</v>
       </c>
       <c r="S21" t="n">
-        <v>-27.1593</v>
+        <v>-6.020400000000004</v>
       </c>
       <c r="T21" t="n">
-        <v>-7.077699999999998</v>
+        <v>-0.2257999999999987</v>
       </c>
       <c r="U21" t="n">
-        <v>-20.0814</v>
+        <v>-5.7942</v>
       </c>
       <c r="V21" t="n">
         <v>79.1615</v>
